--- a/helloworld.xlsx
+++ b/helloworld.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t xml:space="preserve">.特别注意：导入数值加逗号格式，很经常被Excel带成数值，可在前面加个'号，或设置单元格格式为文本			
 .导入规则：
@@ -62,6 +62,9 @@
     <t>2022-12-09</t>
   </si>
   <si>
+    <t>网址</t>
+  </si>
+  <si>
     <t>h</t>
   </si>
   <si>
@@ -81,6 +84,9 @@
   </si>
   <si>
     <t>true</t>
+  </si>
+  <si>
+    <t>https://www.douyacun.com</t>
   </si>
   <si>
     <t>o</t>
@@ -401,7 +407,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <dimension ref="A1"/>
   <sheetData>
     <row r="1">
@@ -510,51 +516,60 @@
       <c r="I8" t="s">
         <v>11</v>
       </c>
+      <c r="J8" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F9" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="J9" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" t="s">
         <v>18</v>
-      </c>
-      <c r="D10" t="s">
-        <v>16</v>
-      </c>
-      <c r="E10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G10" t="s">
-        <v>16</v>
-      </c>
-      <c r="H10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I10" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -563,5 +578,10 @@
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="D7:I7"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="J8" r:id="rId1"/>
+    <hyperlink ref="J9" r:id="rId2"/>
+    <hyperlink ref="J10" r:id="rId3"/>
+  </hyperlinks>
 </worksheet>
 </file>